--- a/NanoAnalyzer_Test_Summary.xlsx
+++ b/NanoAnalyzer_Test_Summary.xlsx
@@ -542,7 +542,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Comprehensive Quality Assurance Evaluation • Executed 2026-09-16 15:10:39 IST</t>
+          <t>Comprehensive Quality Assurance Evaluation • Executed 2026-10-02 17:03:47 IST</t>
         </is>
       </c>
     </row>
@@ -581,17 +581,17 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>175</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>175</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>175</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>0</v>
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>0</v>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F19" s="11" t="n">
         <v>0</v>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>0</v>
@@ -1086,13 +1086,13 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" s="8" t="n">
         <v>0</v>
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>0</v>
